--- a/excel-files/QUEZON CITY/NEW ERA HIGH SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/NEW ERA HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5F87354-C2D2-4615-BCCD-4B2368BA46B9}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7345F572-8968-435C-9624-B752450857B3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="91">
   <si>
     <t>Grade Level</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>Music and Arts</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>VE</t>
@@ -625,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -736,6 +739,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,12 +757,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3464,7 +3468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3473,6 +3477,7 @@
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
@@ -4381,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:10" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4401,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:10" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4411,187 +4416,282 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:10" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="12"/>
+      <c r="C51" s="10">
+        <v>737</v>
+      </c>
+      <c r="D51" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E51" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G51" s="3">
         <f t="shared" ref="G51:G59" si="10">IF((C51-D51)&lt;0,0,C51-D51)</f>
         <v>0</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J51" s="42">
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="12"/>
+      <c r="C52" s="10">
+        <v>737</v>
+      </c>
+      <c r="D52" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E52" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J52" s="42">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="12"/>
+      <c r="C53" s="10">
+        <v>737</v>
+      </c>
+      <c r="D53" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E53" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G53" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H53" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J53" s="42">
+        <v>45476</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="10">
+        <v>737</v>
+      </c>
+      <c r="D54" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J54" s="42">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="12"/>
+      <c r="C55" s="10">
+        <v>737</v>
+      </c>
+      <c r="D55" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E55" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G55" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H55" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J55">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="12"/>
+      <c r="C56" s="10">
+        <v>737</v>
+      </c>
+      <c r="D56" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E56" s="10">
+        <v>2024</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G56" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H56" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J56" s="42">
+        <v>45544</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="12"/>
+      <c r="C57" s="10">
+        <v>737</v>
+      </c>
+      <c r="D57" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E57" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H57" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J57" s="42">
+        <v>45701</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="C58" s="10">
+        <v>737</v>
+      </c>
+      <c r="D58" s="10">
+        <v>1050</v>
+      </c>
       <c r="E58" s="10"/>
-      <c r="F58" s="12"/>
+      <c r="F58" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H58" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J58" s="42">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="12"/>
+      <c r="C59" s="10">
+        <v>737</v>
+      </c>
+      <c r="D59" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H59" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+        <v>313</v>
+      </c>
+      <c r="J59" s="42">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4601,7 +4701,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:10" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4611,7 +4711,9 @@
       <c r="C61" s="10">
         <v>791</v>
       </c>
-      <c r="D61" s="10"/>
+      <c r="D61" s="10">
+        <v>0</v>
+      </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
@@ -4623,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:10" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4633,7 +4735,9 @@
       <c r="C62" s="10">
         <v>791</v>
       </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="10">
+        <v>0</v>
+      </c>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
@@ -4645,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:10" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4655,51 +4759,71 @@
       <c r="C63" s="10">
         <v>791</v>
       </c>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="12"/>
+      <c r="D63" s="10">
+        <v>723</v>
+      </c>
+      <c r="E63" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
-        <v>791</v>
+        <v>68</v>
       </c>
       <c r="H63" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+      <c r="J63" s="42">
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C64" s="10">
         <v>791</v>
       </c>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="12"/>
+      <c r="D64" s="10">
+        <v>723</v>
+      </c>
+      <c r="E64" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
-        <v>791</v>
+        <v>68</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+      <c r="J64" s="42">
+        <v>45905</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="27.75" customHeight="1">
       <c r="A65" s="10">
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C65" s="10">
         <v>791</v>
       </c>
-      <c r="D65" s="10"/>
+      <c r="D65" s="10">
+        <v>0</v>
+      </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
       <c r="G65" s="3">
@@ -4711,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:10" ht="27.75" customHeight="1">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4721,19 +4845,26 @@
       <c r="C66" s="10">
         <v>791</v>
       </c>
-      <c r="D66" s="10"/>
+      <c r="D66" s="10">
+        <v>723</v>
+      </c>
       <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
+      <c r="F66" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>791</v>
+        <v>68</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+      <c r="J66" s="42">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="27.75" customHeight="1">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4743,7 +4874,9 @@
       <c r="C67" s="10">
         <v>791</v>
       </c>
-      <c r="D67" s="10"/>
+      <c r="D67" s="10">
+        <v>0</v>
+      </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
       <c r="G67" s="3">
@@ -4755,17 +4888,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:10" ht="27.75" customHeight="1">
       <c r="A68" s="10">
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C68" s="10">
         <v>791</v>
       </c>
-      <c r="D68" s="10"/>
+      <c r="D68" s="10">
+        <v>0</v>
+      </c>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
       <c r="G68" s="3">
@@ -4777,7 +4912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:10" ht="27.75" customHeight="1">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4787,7 +4922,9 @@
       <c r="C69" s="10">
         <v>791</v>
       </c>
-      <c r="D69" s="10"/>
+      <c r="D69" s="10">
+        <v>0</v>
+      </c>
       <c r="E69" s="10"/>
       <c r="F69" s="12"/>
       <c r="G69" s="3">
@@ -4799,7 +4936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:10" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4809,7 +4946,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:10" ht="27.75" customHeight="1">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4831,7 +4968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:10" ht="27.75" customHeight="1">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4853,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:10" ht="27.75" customHeight="1">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4875,12 +5012,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:10" ht="27.75" customHeight="1">
       <c r="A74" s="10">
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C74" s="10">
         <v>683</v>
@@ -4897,12 +5034,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:10" ht="27.75" customHeight="1">
       <c r="A75" s="10">
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10">
         <v>683</v>
@@ -4919,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:10" ht="27.75" customHeight="1">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4941,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:10" ht="27.75" customHeight="1">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -4963,12 +5100,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:10" ht="27.75" customHeight="1">
       <c r="A78" s="10">
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C78" s="10">
         <v>683</v>
@@ -4985,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:10" ht="27.75" customHeight="1">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5007,7 +5144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:10" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5017,7 +5154,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:10" ht="27.75" customHeight="1">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5039,7 +5176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:10" ht="27.75" customHeight="1">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5061,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:10" ht="27.75" customHeight="1">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5083,12 +5220,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:10" ht="27.75" customHeight="1">
       <c r="A84" s="10">
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" s="10">
         <v>690</v>
@@ -5105,12 +5242,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:10" ht="27.75" customHeight="1">
       <c r="A85" s="10">
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C85" s="10">
         <v>690</v>
@@ -5127,7 +5264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:10" ht="27.75" customHeight="1">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5149,7 +5286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:10" ht="27.75" customHeight="1">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5171,12 +5308,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:10" ht="27.75" customHeight="1">
       <c r="A88" s="10">
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C88" s="10">
         <v>690</v>
@@ -5193,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:10" ht="27.75" customHeight="1">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5215,7 +5352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:10" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5225,12 +5362,12 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:10" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C91" s="1">
         <v>445</v>
@@ -5247,12 +5384,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:10" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1">
         <v>455</v>
@@ -5269,122 +5406,167 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:10" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1">
         <v>455</v>
       </c>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="5"/>
+      <c r="D93" s="1">
+        <v>397</v>
+      </c>
+      <c r="E93" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G93" s="3">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>58</v>
       </c>
       <c r="H93" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+      <c r="J93" s="42">
+        <v>45509</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1">
         <v>455</v>
       </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="5"/>
+      <c r="D94" s="1">
+        <v>397</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G94" s="3">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>58</v>
       </c>
       <c r="H94" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+      <c r="J94" s="42">
+        <v>45730</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C95" s="1">
         <v>455</v>
       </c>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="5"/>
+      <c r="D95" s="1">
+        <v>397</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G95" s="3">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>58</v>
       </c>
       <c r="H95" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+      <c r="J95" s="42">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" s="1">
         <v>455</v>
       </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="5"/>
+      <c r="D96" s="1">
+        <v>397</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G96" s="3">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>58</v>
       </c>
       <c r="H96" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+      <c r="J96" s="42">
+        <v>45770</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C97" s="1">
         <v>455</v>
       </c>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="5"/>
+      <c r="D97" s="1">
+        <v>397</v>
+      </c>
+      <c r="E97" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G97" s="3">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>58</v>
       </c>
       <c r="H97" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+      <c r="J97" s="42">
+        <v>45762</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1">
         <v>455</v>
@@ -5407,12 +5589,18 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{825FF4A3-1D3F-4E16-BFF1-C716239F51EF}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{99D4F661-59B6-4F9A-9E7A-AC693132CCA3}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5424,7 +5612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5454,38 +5642,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5498,81 +5686,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>46</v>
       </c>
+      <c r="N2" s="40" t="s">
+        <v>47</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y2" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>58</v>
       </c>
+      <c r="Z2" s="41" t="s">
+        <v>59</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -6137,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6702,7 +6890,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -7337,7 +7525,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -9532,7 +9720,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -9808,7 +9996,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -10167,7 +10355,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10236,7 +10424,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10443,7 +10631,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10802,7 +10990,7 @@
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -10871,7 +11059,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -11078,7 +11266,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11437,7 +11625,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11506,7 +11694,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11713,7 +11901,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -11862,10 +12050,10 @@
     </row>
     <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -11931,10 +12119,10 @@
     </row>
     <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12000,10 +12188,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12069,10 +12257,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12138,10 +12326,10 @@
     </row>
     <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12207,10 +12395,10 @@
     </row>
     <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12276,10 +12464,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12345,10 +12533,10 @@
     </row>
     <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13410,186 +13598,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13605,15 +13613,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{05F08435-6C68-4ABE-AC24-BD87EBCE357A}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13628,7 +13639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13658,38 +13669,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13702,76 +13713,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>72</v>
       </c>
+      <c r="N2" s="40" t="s">
+        <v>73</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>84</v>
       </c>
+      <c r="Z2" s="41" t="s">
+        <v>85</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -14262,7 +14273,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14815,7 +14826,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -15437,7 +15448,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15921,7 +15932,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15990,7 +16001,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16128,7 +16139,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16197,7 +16208,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16681,7 +16692,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16750,7 +16761,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16888,7 +16899,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16957,7 +16968,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17441,7 +17452,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17510,7 +17521,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17648,7 +17659,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17717,7 +17728,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17994,7 +18005,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18201,7 +18212,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18270,7 +18281,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18339,7 +18350,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18408,7 +18419,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18477,7 +18488,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18754,7 +18765,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -18823,7 +18834,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -18961,7 +18972,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19030,7 +19041,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19099,7 +19110,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19168,7 +19179,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19237,7 +19248,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19514,7 +19525,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19583,7 +19594,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19721,7 +19732,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19790,7 +19801,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19859,7 +19870,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19928,7 +19939,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19997,7 +20008,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20274,7 +20285,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20343,7 +20354,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20481,7 +20492,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20550,7 +20561,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20619,7 +20630,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20688,7 +20699,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20757,7 +20768,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20824,10 +20835,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -20893,10 +20904,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20962,10 +20973,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21031,10 +21042,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21100,10 +21111,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21169,10 +21180,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21238,10 +21249,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21307,10 +21318,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21885,186 +21896,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22082,8 +21913,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L115:L122 R115:R122 X115:X122 R103:R113 L103:L113 F103:F113 F115:F122 L91:L101 R91:R101 X91:X101 X103:X113 R79:R89 L79:L89 F79:F89 F91:F101 L67:L77 R67:R77 X67:X77 X79:X89 R55:R65 L55:L65 F55:F65 F67:F77 L43:L53 R43:R53 X43:X53 X55:X65 R31:R41 L31:L41 F31:F41 F43:F53 L21:L29 R21:R29 X21:X29 X31:X41 R12:R19 L12:L19 F12:F19 F21:F29 F3:F10 L3:L10 R3:R10 X3:X10 X12:X19" xr:uid="{39EA5D97-B72A-4AE5-8BCD-AD80916E25A3}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
